--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf33dbca9c1c47af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51d82be2afe24a73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf863d72775884947"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb7d4429dda492e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R51d82be2afe24a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb584c93632dd456f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb7d4429dda492e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2b283d8e73b4b19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb584c93632dd456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1af531de4e1f4268"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2b283d8e73b4b19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceb52a333b80490e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1af531de4e1f4268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9707b2f5fe304de6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rceb52a333b80490e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R601c1841fdcd4302"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9707b2f5fe304de6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6ca263b0a5b4c02"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R601c1841fdcd4302"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf553bb060943aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re6ca263b0a5b4c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0439366ff22d455d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bf553bb060943aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a5e719286744e06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0439366ff22d455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree96d0006b764fee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a5e719286744e06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149ec746833e432f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree96d0006b764fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd22e49be9d9d4303"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149ec746833e432f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ebc55f75359438e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd22e49be9d9d4303"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd36dd8b55dfd4543"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ebc55f75359438e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c4d15e955b9469f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd36dd8b55dfd4543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d1de81500b54c97"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c4d15e955b9469f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ec081b3bbf4c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d1de81500b54c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11642f0fe7be41b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ec081b3bbf4c59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0184267b2b8c40a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11642f0fe7be41b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R987193dfd5c84d43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0184267b2b8c40a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e85fd7763d1475d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R987193dfd5c84d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R440c4a3822b144af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e85fd7763d1475d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b74cb9c2e284a5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/TableWithCalculatedColumn/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R440c4a3822b144af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95e75f3a644c48ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -103,7 +103,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b74cb9c2e284a5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53631c0978db45d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>